--- a/2d/results/best_unet_filter_projection_mean/best_unet.xlsx
+++ b/2d/results/best_unet_filter_projection_mean/best_unet.xlsx
@@ -535,10 +535,10 @@
         <v>140</v>
       </c>
       <c r="C2" t="n">
-        <v>9.960641301922472</v>
+        <v>17.26683635589969</v>
       </c>
       <c r="D2" t="n">
-        <v>17.26683715762273</v>
+        <v>9.960641882666774</v>
       </c>
       <c r="E2" t="n">
         <v>16.48624936168851</v>
@@ -596,10 +596,10 @@
         <v>141</v>
       </c>
       <c r="C3" t="n">
-        <v>5.799653714554043</v>
+        <v>13.08177212541448</v>
       </c>
       <c r="D3" t="n">
-        <v>13.08177201976891</v>
+        <v>5.799654205653648</v>
       </c>
       <c r="E3" t="n">
         <v>26.64504063529104</v>
@@ -657,10 +657,10 @@
         <v>149</v>
       </c>
       <c r="C4" t="n">
-        <v>7.504124525695822</v>
+        <v>9.141333981099722</v>
       </c>
       <c r="D4" t="n">
-        <v>9.141334433283207</v>
+        <v>7.504124185555359</v>
       </c>
       <c r="E4" t="n">
         <v>15.66711742168132</v>
@@ -718,10 +718,10 @@
         <v>160</v>
       </c>
       <c r="C5" t="n">
-        <v>11.89858768255132</v>
+        <v>16.15717351172762</v>
       </c>
       <c r="D5" t="n">
-        <v>16.15717244761474</v>
+        <v>11.89858889616212</v>
       </c>
       <c r="E5" t="n">
         <v>31.93707489464807</v>
@@ -779,10 +779,10 @@
         <v>170</v>
       </c>
       <c r="C6" t="n">
-        <v>4.931303949965791</v>
+        <v>14.49999923023781</v>
       </c>
       <c r="D6" t="n">
-        <v>14.49999922986447</v>
+        <v>4.931303884705897</v>
       </c>
       <c r="E6" t="n">
         <v>17.4557046261906</v>
@@ -840,10 +840,10 @@
         <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>10.36803596265674</v>
+        <v>11.67639714133106</v>
       </c>
       <c r="D7" t="n">
-        <v>11.67639893354524</v>
+        <v>10.36803652843212</v>
       </c>
       <c r="E7" t="n">
         <v>23.53030699293057</v>
@@ -901,10 +901,10 @@
         <v>190</v>
       </c>
       <c r="C8" t="n">
-        <v>6.356089798638186</v>
+        <v>11.48914164846039</v>
       </c>
       <c r="D8" t="n">
-        <v>11.48914156835117</v>
+        <v>6.356090257151815</v>
       </c>
       <c r="E8" t="n">
         <v>31.18077765179081</v>
@@ -962,10 +962,10 @@
         <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>13.57775262739598</v>
+        <v>21.59887332822754</v>
       </c>
       <c r="D9" t="n">
-        <v>21.59887276243198</v>
+        <v>13.57775306737694</v>
       </c>
       <c r="E9" t="n">
         <v>20.64468102444152</v>
@@ -1023,10 +1023,10 @@
         <v>199</v>
       </c>
       <c r="C10" t="n">
-        <v>8.770614872997283</v>
+        <v>13.72760142787309</v>
       </c>
       <c r="D10" t="n">
-        <v>13.72760116193403</v>
+        <v>8.770615105945984</v>
       </c>
       <c r="E10" t="n">
         <v>29.60549914709465</v>
@@ -1084,10 +1084,10 @@
         <v>100</v>
       </c>
       <c r="C11" t="n">
-        <v>8.149460637215714</v>
+        <v>17.50977840842392</v>
       </c>
       <c r="D11" t="n">
-        <v>17.50977706751593</v>
+        <v>8.149460508249669</v>
       </c>
       <c r="E11" t="n">
         <v>18.50072254335259</v>
@@ -1145,10 +1145,10 @@
         <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>5.660615163345213</v>
+        <v>15.03829134702332</v>
       </c>
       <c r="D12" t="n">
-        <v>15.03829171428218</v>
+        <v>5.660615051273542</v>
       </c>
       <c r="E12" t="n">
         <v>18.81038582552551</v>
@@ -1206,10 +1206,10 @@
         <v>111</v>
       </c>
       <c r="C13" t="n">
-        <v>6.657755150396612</v>
+        <v>10.18524538409196</v>
       </c>
       <c r="D13" t="n">
-        <v>10.18524580494627</v>
+        <v>6.657754782434099</v>
       </c>
       <c r="E13" t="n">
         <v>20.09641306993106</v>
@@ -1267,10 +1267,10 @@
         <v>135</v>
       </c>
       <c r="C14" t="n">
-        <v>9.897193049500236</v>
+        <v>18.26445795283155</v>
       </c>
       <c r="D14" t="n">
-        <v>18.26445804544271</v>
+        <v>9.897192963121096</v>
       </c>
       <c r="E14" t="n">
         <v>23.48875897660984</v>
@@ -1328,10 +1328,10 @@
         <v>990</v>
       </c>
       <c r="C15" t="n">
-        <v>8.30541543493897</v>
+        <v>14.16272514797404</v>
       </c>
       <c r="D15" t="n">
-        <v>14.16272464566204</v>
+        <v>8.305415358059044</v>
       </c>
       <c r="E15" t="n">
         <v>27.14673439025135</v>
@@ -1389,10 +1389,10 @@
         <v>920</v>
       </c>
       <c r="C16" t="n">
-        <v>11.74628639265405</v>
+        <v>20.13532228727027</v>
       </c>
       <c r="D16" t="n">
-        <v>20.13532526237125</v>
+        <v>11.74628511910083</v>
       </c>
       <c r="E16" t="n">
         <v>23.62311418179442</v>

--- a/2d/results/best_unet_filter_projection_mean/best_unet.xlsx
+++ b/2d/results/best_unet_filter_projection_mean/best_unet.xlsx
@@ -535,55 +535,55 @@
         <v>140</v>
       </c>
       <c r="C2" t="n">
-        <v>17.26683635589969</v>
+        <v>23.14541423201783</v>
       </c>
       <c r="D2" t="n">
-        <v>9.960641882666774</v>
+        <v>8.889777079176884</v>
       </c>
       <c r="E2" t="n">
-        <v>16.48624936168851</v>
+        <v>14.4941084960098</v>
       </c>
       <c r="F2" t="n">
-        <v>12.316</v>
+        <v>14.31325</v>
       </c>
       <c r="G2" t="n">
-        <v>10.28025</v>
+        <v>12.23325</v>
       </c>
       <c r="H2" t="n">
-        <v>75.12553686378146</v>
+        <v>82.62220712771054</v>
       </c>
       <c r="I2" t="n">
-        <v>72.22028772926245</v>
+        <v>72.42932557249701</v>
       </c>
       <c r="J2" t="n">
-        <v>63.59231501141612</v>
+        <v>67.91857822499315</v>
       </c>
       <c r="K2" t="n">
-        <v>63.47407358266508</v>
+        <v>67.46884810401764</v>
       </c>
       <c r="L2" t="n">
-        <v>36.88864598371465</v>
+        <v>41.79810574943927</v>
       </c>
       <c r="M2" t="n">
-        <v>30.28729902813674</v>
+        <v>35.3005966102924</v>
       </c>
       <c r="N2" t="n">
-        <v>71.68156654051937</v>
+        <v>75.349330273381</v>
       </c>
       <c r="O2" t="n">
-        <v>60.91016289004232</v>
+        <v>64.66868966870712</v>
       </c>
       <c r="P2" t="n">
-        <v>15.30992870292388</v>
+        <v>17.76724553299469</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.73283234957625</v>
+        <v>12.66793947589704</v>
       </c>
       <c r="R2" t="n">
-        <v>12.08563540174239</v>
+        <v>6.819085563183734</v>
       </c>
       <c r="S2" t="n">
-        <v>15.00449652664316</v>
+        <v>14.15174037125017</v>
       </c>
     </row>
     <row r="3">
@@ -596,55 +596,55 @@
         <v>141</v>
       </c>
       <c r="C3" t="n">
-        <v>13.08177212541448</v>
+        <v>17.98339268175267</v>
       </c>
       <c r="D3" t="n">
-        <v>5.799654205653648</v>
+        <v>5.487224020545667</v>
       </c>
       <c r="E3" t="n">
-        <v>26.64504063529104</v>
+        <v>26.12896110793135</v>
       </c>
       <c r="F3" t="n">
-        <v>21.32025000000001</v>
+        <v>25.60074999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>15.63275000000001</v>
+        <v>18.8885</v>
       </c>
       <c r="H3" t="n">
-        <v>80.39933361583459</v>
+        <v>92.97583078081756</v>
       </c>
       <c r="I3" t="n">
-        <v>87.3447580988562</v>
+        <v>90.10798713528678</v>
       </c>
       <c r="J3" t="n">
-        <v>71.06695918264364</v>
+        <v>77.89130974482853</v>
       </c>
       <c r="K3" t="n">
-        <v>77.29137269615197</v>
+        <v>80.3662991900745</v>
       </c>
       <c r="L3" t="n">
-        <v>54.61919951981804</v>
+        <v>59.92793123444725</v>
       </c>
       <c r="M3" t="n">
-        <v>43.88832581828978</v>
+        <v>49.22568826023426</v>
       </c>
       <c r="N3" t="n">
-        <v>79.45972747259916</v>
+        <v>86.58687643666319</v>
       </c>
       <c r="O3" t="n">
-        <v>70.75698131760666</v>
+        <v>75.48585236743165</v>
       </c>
       <c r="P3" t="n">
-        <v>11.59771140019848</v>
+        <v>16.21379706729705</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.5518637467513</v>
+        <v>13.55608671404408</v>
       </c>
       <c r="R3" t="n">
-        <v>11.50613849698252</v>
+        <v>10.81142665648462</v>
       </c>
       <c r="S3" t="n">
-        <v>10.94595190233954</v>
+        <v>12.80986916559704</v>
       </c>
     </row>
     <row r="4">
@@ -657,55 +657,55 @@
         <v>149</v>
       </c>
       <c r="C4" t="n">
-        <v>9.141333981099722</v>
+        <v>10.7203705103444</v>
       </c>
       <c r="D4" t="n">
-        <v>7.504124185555359</v>
+        <v>10.13389013438354</v>
       </c>
       <c r="E4" t="n">
-        <v>15.66711742168132</v>
+        <v>15.90119142628591</v>
       </c>
       <c r="F4" t="n">
-        <v>11.04666666666667</v>
+        <v>12.88125</v>
       </c>
       <c r="G4" t="n">
-        <v>9.312083333333335</v>
+        <v>10.82583333333333</v>
       </c>
       <c r="H4" t="n">
-        <v>81.31495007901211</v>
+        <v>85.70624803527896</v>
       </c>
       <c r="I4" t="n">
-        <v>73.77873793764381</v>
+        <v>71.48370010914908</v>
       </c>
       <c r="J4" t="n">
-        <v>71.50922134946649</v>
+        <v>76.4141938914711</v>
       </c>
       <c r="K4" t="n">
-        <v>63.90264984362727</v>
+        <v>60.33196238660702</v>
       </c>
       <c r="L4" t="n">
-        <v>33.05517970119779</v>
+        <v>38.89897807561371</v>
       </c>
       <c r="M4" t="n">
-        <v>27.54254262810207</v>
+        <v>33.67521427403626</v>
       </c>
       <c r="N4" t="n">
-        <v>76.30380694589688</v>
+        <v>76.76820994157632</v>
       </c>
       <c r="O4" t="n">
-        <v>65.95597950515072</v>
+        <v>66.15652426470781</v>
       </c>
       <c r="P4" t="n">
-        <v>12.04844424633522</v>
+        <v>10.84339508903763</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.68168977934911</v>
+        <v>12.99834145506855</v>
       </c>
       <c r="R4" t="n">
-        <v>13.38100003715887</v>
+        <v>15.57685119390806</v>
       </c>
       <c r="S4" t="n">
-        <v>13.55217890087417</v>
+        <v>13.82015621547188</v>
       </c>
     </row>
     <row r="5">
@@ -718,55 +718,55 @@
         <v>160</v>
       </c>
       <c r="C5" t="n">
-        <v>16.15717351172762</v>
+        <v>17.73022721742787</v>
       </c>
       <c r="D5" t="n">
-        <v>11.89858889616212</v>
+        <v>8.988340713534553</v>
       </c>
       <c r="E5" t="n">
-        <v>31.93707489464807</v>
+        <v>18.37602523713418</v>
       </c>
       <c r="F5" t="n">
-        <v>10.86125</v>
+        <v>13.91000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>7.393750000000002</v>
+        <v>11.3575</v>
       </c>
       <c r="H5" t="n">
-        <v>67.212811613987</v>
+        <v>78.62239773414059</v>
       </c>
       <c r="I5" t="n">
-        <v>66.59382228639457</v>
+        <v>69.87773841065177</v>
       </c>
       <c r="J5" t="n">
-        <v>52.95560074627652</v>
+        <v>64.02068411059766</v>
       </c>
       <c r="K5" t="n">
-        <v>51.40450909570603</v>
+        <v>58.36786042551622</v>
       </c>
       <c r="L5" t="n">
-        <v>35.91457920875735</v>
+        <v>42.9509494371914</v>
       </c>
       <c r="M5" t="n">
-        <v>29.08312880059331</v>
+        <v>36.16168843340895</v>
       </c>
       <c r="N5" t="n">
-        <v>64.91920338754835</v>
+        <v>71.67871900929201</v>
       </c>
       <c r="O5" t="n">
-        <v>50.018926381959</v>
+        <v>58.16712361865941</v>
       </c>
       <c r="P5" t="n">
-        <v>21.13481247408732</v>
+        <v>18.58108180070391</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.9864700196794</v>
+        <v>17.60281285847821</v>
       </c>
       <c r="R5" t="n">
-        <v>22.81462823965714</v>
+        <v>16.50265034852575</v>
       </c>
       <c r="S5" t="n">
-        <v>22.92387110919312</v>
+        <v>18.86518588063035</v>
       </c>
     </row>
     <row r="6">
@@ -779,55 +779,55 @@
         <v>170</v>
       </c>
       <c r="C6" t="n">
-        <v>14.49999923023781</v>
+        <v>15.65458468590464</v>
       </c>
       <c r="D6" t="n">
-        <v>4.931303884705897</v>
+        <v>9.936341096569503</v>
       </c>
       <c r="E6" t="n">
-        <v>17.4557046261906</v>
+        <v>13.99839390950252</v>
       </c>
       <c r="F6" t="n">
-        <v>14.73250000000001</v>
+        <v>17.22000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>12.160625</v>
+        <v>14.81</v>
       </c>
       <c r="H6" t="n">
-        <v>80.52384479350224</v>
+        <v>92.17863326905822</v>
       </c>
       <c r="I6" t="n">
-        <v>73.08327372766158</v>
+        <v>78.16094515512879</v>
       </c>
       <c r="J6" t="n">
-        <v>61.54946967578401</v>
+        <v>66.36924520629996</v>
       </c>
       <c r="K6" t="n">
-        <v>64.41758513699887</v>
+        <v>61.1562745422887</v>
       </c>
       <c r="L6" t="n">
-        <v>42.35094784600919</v>
+        <v>51.73544849729637</v>
       </c>
       <c r="M6" t="n">
-        <v>38.26758857830011</v>
+        <v>43.72655563015815</v>
       </c>
       <c r="N6" t="n">
-        <v>72.71006630245273</v>
+        <v>81.1202837575115</v>
       </c>
       <c r="O6" t="n">
-        <v>59.55451594565574</v>
+        <v>58.7508442158821</v>
       </c>
       <c r="P6" t="n">
-        <v>23.52975720292584</v>
+        <v>27.98940239536222</v>
       </c>
       <c r="Q6" t="n">
-        <v>17.94972317258734</v>
+        <v>25.09283685988456</v>
       </c>
       <c r="R6" t="n">
-        <v>11.80164337934306</v>
+        <v>21.66044165862579</v>
       </c>
       <c r="S6" t="n">
-        <v>18.08801636307142</v>
+        <v>27.57099254860092</v>
       </c>
     </row>
     <row r="7">
@@ -840,55 +840,55 @@
         <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>11.67639714133106</v>
+        <v>10.93329262696186</v>
       </c>
       <c r="D7" t="n">
-        <v>10.36803652843212</v>
+        <v>11.02225301702064</v>
       </c>
       <c r="E7" t="n">
-        <v>23.53030699293057</v>
+        <v>25.99225541261455</v>
       </c>
       <c r="F7" t="n">
-        <v>12.16</v>
+        <v>14.55666666666667</v>
       </c>
       <c r="G7" t="n">
-        <v>9.266250000000005</v>
+        <v>10.80625000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>75.8447210795489</v>
+        <v>81.82764526381679</v>
       </c>
       <c r="I7" t="n">
-        <v>73.12973461971696</v>
+        <v>73.32324319219681</v>
       </c>
       <c r="J7" t="n">
-        <v>65.00047713834356</v>
+        <v>71.84794665922426</v>
       </c>
       <c r="K7" t="n">
-        <v>62.80319315883867</v>
+        <v>63.525718007104</v>
       </c>
       <c r="L7" t="n">
-        <v>34.5551121835975</v>
+        <v>40.55120137666709</v>
       </c>
       <c r="M7" t="n">
-        <v>27.97041743202969</v>
+        <v>32.52902085833315</v>
       </c>
       <c r="N7" t="n">
-        <v>72.36766904917948</v>
+        <v>74.29124146546714</v>
       </c>
       <c r="O7" t="n">
-        <v>62.64284437525285</v>
+        <v>66.85832661261932</v>
       </c>
       <c r="P7" t="n">
-        <v>14.09468378152858</v>
+        <v>12.00841234540675</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.15260045475293</v>
+        <v>12.65222706287586</v>
       </c>
       <c r="R7" t="n">
-        <v>14.11805398043635</v>
+        <v>13.37027311258115</v>
       </c>
       <c r="S7" t="n">
-        <v>13.34026235001334</v>
+        <v>9.915566325111202</v>
       </c>
     </row>
     <row r="8">
@@ -901,55 +901,55 @@
         <v>190</v>
       </c>
       <c r="C8" t="n">
-        <v>11.48914164846039</v>
+        <v>14.67039529370194</v>
       </c>
       <c r="D8" t="n">
-        <v>6.356090257151815</v>
+        <v>6.713990441400239</v>
       </c>
       <c r="E8" t="n">
-        <v>31.18077765179081</v>
+        <v>22.33641628297107</v>
       </c>
       <c r="F8" t="n">
-        <v>16.446875</v>
+        <v>19.80500000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>11.31687499999999</v>
+        <v>15.38125</v>
       </c>
       <c r="H8" t="n">
-        <v>89.98177239080886</v>
+        <v>101.3718402713495</v>
       </c>
       <c r="I8" t="n">
-        <v>83.10487268098981</v>
+        <v>86.4223791331399</v>
       </c>
       <c r="J8" t="n">
-        <v>68.6814229302658</v>
+        <v>80.65409369927511</v>
       </c>
       <c r="K8" t="n">
-        <v>70.12894710990578</v>
+        <v>75.52125948014776</v>
       </c>
       <c r="L8" t="n">
-        <v>39.94191366484689</v>
+        <v>46.18591973544677</v>
       </c>
       <c r="M8" t="n">
-        <v>33.49059916161824</v>
+        <v>40.778115238889</v>
       </c>
       <c r="N8" t="n">
-        <v>84.28275746620024</v>
+        <v>91.3148326634134</v>
       </c>
       <c r="O8" t="n">
-        <v>67.57036329100879</v>
+        <v>75.56266975715457</v>
       </c>
       <c r="P8" t="n">
-        <v>23.67083642293441</v>
+        <v>20.43737838498115</v>
       </c>
       <c r="Q8" t="n">
-        <v>19.80002456951541</v>
+        <v>16.83640471656063</v>
       </c>
       <c r="R8" t="n">
-        <v>15.60791779229783</v>
+        <v>12.61164721682533</v>
       </c>
       <c r="S8" t="n">
-        <v>19.82668316714525</v>
+        <v>17.24999000386362</v>
       </c>
     </row>
     <row r="9">
@@ -962,55 +962,55 @@
         <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>21.59887332822754</v>
+        <v>23.70383057628247</v>
       </c>
       <c r="D9" t="n">
-        <v>13.57775306737694</v>
+        <v>11.99163217451634</v>
       </c>
       <c r="E9" t="n">
-        <v>20.64468102444152</v>
+        <v>14.66005493455415</v>
       </c>
       <c r="F9" t="n">
-        <v>13.96458333333333</v>
+        <v>16.31583333333333</v>
       </c>
       <c r="G9" t="n">
-        <v>11.09166666666667</v>
+        <v>13.92083333333334</v>
       </c>
       <c r="H9" t="n">
-        <v>82.37750796584595</v>
+        <v>91.80003189007665</v>
       </c>
       <c r="I9" t="n">
-        <v>75.66577066263976</v>
+        <v>79.72391501441484</v>
       </c>
       <c r="J9" t="n">
-        <v>69.25159740429518</v>
+        <v>75.63873926436936</v>
       </c>
       <c r="K9" t="n">
-        <v>64.58708486998965</v>
+        <v>67.79667712675014</v>
       </c>
       <c r="L9" t="n">
-        <v>38.10081984438037</v>
+        <v>44.29828948734438</v>
       </c>
       <c r="M9" t="n">
-        <v>33.93482440815904</v>
+        <v>38.14318749217236</v>
       </c>
       <c r="N9" t="n">
-        <v>76.90259040981208</v>
+        <v>83.51182668232542</v>
       </c>
       <c r="O9" t="n">
-        <v>64.87784027764347</v>
+        <v>69.08732280353088</v>
       </c>
       <c r="P9" t="n">
-        <v>15.92534049043808</v>
+        <v>17.57693949524748</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.3182278959744</v>
+        <v>16.35770731124164</v>
       </c>
       <c r="R9" t="n">
-        <v>14.64491888185509</v>
+        <v>14.95124753251614</v>
       </c>
       <c r="S9" t="n">
-        <v>15.63695069644559</v>
+        <v>17.25687869321683</v>
       </c>
     </row>
     <row r="10">
@@ -1023,55 +1023,55 @@
         <v>199</v>
       </c>
       <c r="C10" t="n">
-        <v>13.72760142787309</v>
+        <v>16.50028972971138</v>
       </c>
       <c r="D10" t="n">
-        <v>8.770615105945984</v>
+        <v>9.074993246997542</v>
       </c>
       <c r="E10" t="n">
-        <v>29.60549914709465</v>
+        <v>24.38407795357636</v>
       </c>
       <c r="F10" t="n">
-        <v>11.8375</v>
+        <v>14.64583333333333</v>
       </c>
       <c r="G10" t="n">
-        <v>8.220833333333333</v>
+        <v>11.06666666666667</v>
       </c>
       <c r="H10" t="n">
-        <v>78.36465584544571</v>
+        <v>88.79739830889378</v>
       </c>
       <c r="I10" t="n">
-        <v>76.43238560902844</v>
+        <v>81.68348028309374</v>
       </c>
       <c r="J10" t="n">
-        <v>62.97077224812688</v>
+        <v>75.76501142167761</v>
       </c>
       <c r="K10" t="n">
-        <v>65.2165798723378</v>
+        <v>71.6453963321821</v>
       </c>
       <c r="L10" t="n">
-        <v>32.80515054285888</v>
+        <v>37.81699050161533</v>
       </c>
       <c r="M10" t="n">
-        <v>24.95688311273527</v>
+        <v>29.454697058523</v>
       </c>
       <c r="N10" t="n">
-        <v>75.8265771417268</v>
+        <v>83.80635847613632</v>
       </c>
       <c r="O10" t="n">
-        <v>62.61429948252218</v>
+        <v>72.20394500655453</v>
       </c>
       <c r="P10" t="n">
-        <v>19.63502989406404</v>
+        <v>14.6773112157507</v>
       </c>
       <c r="Q10" t="n">
-        <v>17.19306125552328</v>
+        <v>13.52995799314363</v>
       </c>
       <c r="R10" t="n">
-        <v>14.68871047794624</v>
+        <v>12.28582719113331</v>
       </c>
       <c r="S10" t="n">
-        <v>17.42781463852916</v>
+        <v>13.84240709167782</v>
       </c>
     </row>
     <row r="11">
@@ -1084,55 +1084,55 @@
         <v>100</v>
       </c>
       <c r="C11" t="n">
-        <v>17.50977840842392</v>
+        <v>19.02705838246533</v>
       </c>
       <c r="D11" t="n">
-        <v>8.149460508249669</v>
+        <v>10.59967867083313</v>
       </c>
       <c r="E11" t="n">
-        <v>18.50072254335259</v>
+        <v>14.00920695676991</v>
       </c>
       <c r="F11" t="n">
-        <v>14.27</v>
+        <v>18.760625</v>
       </c>
       <c r="G11" t="n">
-        <v>11.618125</v>
+        <v>16.125625</v>
       </c>
       <c r="H11" t="n">
-        <v>82.95275265040812</v>
+        <v>102.4642085673479</v>
       </c>
       <c r="I11" t="n">
-        <v>70.853431704732</v>
+        <v>80.87170034822034</v>
       </c>
       <c r="J11" t="n">
-        <v>68.39669176202086</v>
+        <v>86.80436649350116</v>
       </c>
       <c r="K11" t="n">
-        <v>63.20676498785716</v>
+        <v>70.1035525191952</v>
       </c>
       <c r="L11" t="n">
-        <v>42.6446078345448</v>
+        <v>52.23414436066807</v>
       </c>
       <c r="M11" t="n">
-        <v>33.36391698870965</v>
+        <v>41.54311051151898</v>
       </c>
       <c r="N11" t="n">
-        <v>74.95214999023187</v>
+        <v>89.35783036368514</v>
       </c>
       <c r="O11" t="n">
-        <v>62.5650021572208</v>
+        <v>74.74802946492701</v>
       </c>
       <c r="P11" t="n">
-        <v>17.54574287254166</v>
+        <v>15.28462862881734</v>
       </c>
       <c r="Q11" t="n">
-        <v>14.42873308015752</v>
+        <v>14.41623980933766</v>
       </c>
       <c r="R11" t="n">
-        <v>10.77486049700913</v>
+        <v>13.31324545648997</v>
       </c>
       <c r="S11" t="n">
-        <v>16.51467090601036</v>
+        <v>16.35401915973402</v>
       </c>
     </row>
     <row r="12">
@@ -1145,55 +1145,55 @@
         <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>15.03829134702332</v>
+        <v>25.16263530755493</v>
       </c>
       <c r="D12" t="n">
-        <v>5.660615051273542</v>
+        <v>8.690312513649282</v>
       </c>
       <c r="E12" t="n">
-        <v>18.81038582552551</v>
+        <v>32.16736959961078</v>
       </c>
       <c r="F12" t="n">
-        <v>12.58875</v>
+        <v>13.99437500000001</v>
       </c>
       <c r="G12" t="n">
-        <v>10.214375</v>
+        <v>9.48875</v>
       </c>
       <c r="H12" t="n">
-        <v>70.05724660704394</v>
+        <v>78.92448425182357</v>
       </c>
       <c r="I12" t="n">
-        <v>70.26722202225292</v>
+        <v>70.71421391771247</v>
       </c>
       <c r="J12" t="n">
-        <v>58.39936817116787</v>
+        <v>53.74306513101851</v>
       </c>
       <c r="K12" t="n">
-        <v>61.43346147022309</v>
+        <v>62.73942757394504</v>
       </c>
       <c r="L12" t="n">
-        <v>39.05382129715817</v>
+        <v>41.90589074171824</v>
       </c>
       <c r="M12" t="n">
-        <v>32.8823669742646</v>
+        <v>34.04825560751513</v>
       </c>
       <c r="N12" t="n">
-        <v>65.82381934276393</v>
+        <v>70.8195676978852</v>
       </c>
       <c r="O12" t="n">
-        <v>58.45325252768565</v>
+        <v>56.76720447386233</v>
       </c>
       <c r="P12" t="n">
-        <v>16.62531742017334</v>
+        <v>31.89853582276596</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.58237817908896</v>
+        <v>22.1464974993055</v>
       </c>
       <c r="R12" t="n">
-        <v>12.57420934053668</v>
+        <v>11.2613465937753</v>
       </c>
       <c r="S12" t="n">
-        <v>11.19775966761989</v>
+        <v>19.82035411500401</v>
       </c>
     </row>
     <row r="13">
@@ -1206,55 +1206,55 @@
         <v>111</v>
       </c>
       <c r="C13" t="n">
-        <v>10.18524538409196</v>
+        <v>10.1776556842221</v>
       </c>
       <c r="D13" t="n">
-        <v>6.657754782434099</v>
+        <v>6.037935346784887</v>
       </c>
       <c r="E13" t="n">
-        <v>20.09641306993106</v>
+        <v>14.79806059758452</v>
       </c>
       <c r="F13" t="n">
-        <v>14.773125</v>
+        <v>17.71312500000001</v>
       </c>
       <c r="G13" t="n">
-        <v>11.804375</v>
+        <v>15.09125</v>
       </c>
       <c r="H13" t="n">
-        <v>85.65762737944294</v>
+        <v>91.39294620870294</v>
       </c>
       <c r="I13" t="n">
-        <v>81.09022075195858</v>
+        <v>78.97187077379675</v>
       </c>
       <c r="J13" t="n">
-        <v>76.98944465388347</v>
+        <v>85.08957539466581</v>
       </c>
       <c r="K13" t="n">
-        <v>75.03161187850563</v>
+        <v>73.1710404969464</v>
       </c>
       <c r="L13" t="n">
-        <v>38.03090307242741</v>
+        <v>46.17982500141848</v>
       </c>
       <c r="M13" t="n">
-        <v>30.5130505479938</v>
+        <v>39.72699534965531</v>
       </c>
       <c r="N13" t="n">
-        <v>81.61685508507742</v>
+        <v>82.83205838565387</v>
       </c>
       <c r="O13" t="n">
-        <v>74.16550668255255</v>
+        <v>76.50917356266697</v>
       </c>
       <c r="P13" t="n">
-        <v>10.11935330584013</v>
+        <v>6.89651578133423</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.831628356283804</v>
+        <v>7.104454255036709</v>
       </c>
       <c r="R13" t="n">
-        <v>7.471383797573546</v>
+        <v>7.339042168155275</v>
       </c>
       <c r="S13" t="n">
-        <v>9.12970274512336</v>
+        <v>7.631995269495086</v>
       </c>
     </row>
     <row r="14">
@@ -1267,55 +1267,55 @@
         <v>135</v>
       </c>
       <c r="C14" t="n">
-        <v>18.26445795283155</v>
+        <v>16.91594048280426</v>
       </c>
       <c r="D14" t="n">
-        <v>9.897192963121096</v>
+        <v>11.08293516657838</v>
       </c>
       <c r="E14" t="n">
-        <v>23.48875897660984</v>
+        <v>28.89534878648197</v>
       </c>
       <c r="F14" t="n">
-        <v>12.84208333333334</v>
+        <v>17.0825</v>
       </c>
       <c r="G14" t="n">
-        <v>9.785</v>
+        <v>12.17916666666667</v>
       </c>
       <c r="H14" t="n">
-        <v>75.95696591027702</v>
+        <v>85.73999375179652</v>
       </c>
       <c r="I14" t="n">
-        <v>70.69424127701693</v>
+        <v>77.30234263593043</v>
       </c>
       <c r="J14" t="n">
-        <v>62.33885504918417</v>
+        <v>69.62534436411256</v>
       </c>
       <c r="K14" t="n">
-        <v>59.24944868715077</v>
+        <v>62.67156580668669</v>
       </c>
       <c r="L14" t="n">
-        <v>37.95378471079685</v>
+        <v>47.63417500672836</v>
       </c>
       <c r="M14" t="n">
-        <v>31.62205036336637</v>
+        <v>36.74520433362256</v>
       </c>
       <c r="N14" t="n">
-        <v>71.49154620026185</v>
+        <v>77.2178657571705</v>
       </c>
       <c r="O14" t="n">
-        <v>58.66105389850683</v>
+        <v>63.80762294932055</v>
       </c>
       <c r="P14" t="n">
-        <v>17.84411119849537</v>
+        <v>18.75954223894397</v>
       </c>
       <c r="Q14" t="n">
-        <v>17.05354989353407</v>
+        <v>18.84949078356289</v>
       </c>
       <c r="R14" t="n">
-        <v>16.1983858492137</v>
+        <v>18.9306834640509</v>
       </c>
       <c r="S14" t="n">
-        <v>17.89293004739395</v>
+        <v>17.375376347911</v>
       </c>
     </row>
     <row r="15">
@@ -1328,55 +1328,55 @@
         <v>990</v>
       </c>
       <c r="C15" t="n">
-        <v>14.16272514797404</v>
+        <v>10.99478687825671</v>
       </c>
       <c r="D15" t="n">
-        <v>8.305415358059044</v>
+        <v>5.453276967493752</v>
       </c>
       <c r="E15" t="n">
-        <v>27.14673439025135</v>
+        <v>28.91675535328893</v>
       </c>
       <c r="F15" t="n">
-        <v>13.595625</v>
+        <v>14.75875</v>
       </c>
       <c r="G15" t="n">
-        <v>9.912500000000001</v>
+        <v>10.495</v>
       </c>
       <c r="H15" t="n">
-        <v>71.60260532361437</v>
+        <v>76.77555264740249</v>
       </c>
       <c r="I15" t="n">
-        <v>65.28509123282556</v>
+        <v>65.07404371162237</v>
       </c>
       <c r="J15" t="n">
-        <v>55.21472284006269</v>
+        <v>60.84162543996375</v>
       </c>
       <c r="K15" t="n">
-        <v>57.21930689468761</v>
+        <v>54.09371144769399</v>
       </c>
       <c r="L15" t="n">
-        <v>42.3725840664295</v>
+        <v>47.40525328865425</v>
       </c>
       <c r="M15" t="n">
-        <v>36.70555198620066</v>
+        <v>38.90168692130705</v>
       </c>
       <c r="N15" t="n">
-        <v>65.07262870227871</v>
+        <v>66.15299917061596</v>
       </c>
       <c r="O15" t="n">
-        <v>53.61086066364026</v>
+        <v>53.92014340816554</v>
       </c>
       <c r="P15" t="n">
-        <v>22.83424349225201</v>
+        <v>20.74778078942579</v>
       </c>
       <c r="Q15" t="n">
-        <v>17.85888858441191</v>
+        <v>19.00892247818194</v>
       </c>
       <c r="R15" t="n">
-        <v>12.36565299529366</v>
+        <v>16.85576126409711</v>
       </c>
       <c r="S15" t="n">
-        <v>17.61009520175117</v>
+        <v>18.52377874435587</v>
       </c>
     </row>
     <row r="16">
@@ -1389,55 +1389,55 @@
         <v>920</v>
       </c>
       <c r="C16" t="n">
-        <v>20.13532228727027</v>
+        <v>22.59753841490179</v>
       </c>
       <c r="D16" t="n">
-        <v>11.74628511910083</v>
+        <v>10.76052135203255</v>
       </c>
       <c r="E16" t="n">
-        <v>23.62311418179442</v>
+        <v>25.55123258365024</v>
       </c>
       <c r="F16" t="n">
-        <v>8.354166666666668</v>
+        <v>12.17625</v>
       </c>
       <c r="G16" t="n">
-        <v>6.361666666666664</v>
+        <v>9.049166666666665</v>
       </c>
       <c r="H16" t="n">
-        <v>68.96128501258096</v>
+        <v>83.04225103518787</v>
       </c>
       <c r="I16" t="n">
-        <v>66.58882143357887</v>
+        <v>76.32098806765822</v>
       </c>
       <c r="J16" t="n">
-        <v>49.88462841288006</v>
+        <v>55.13985539732218</v>
       </c>
       <c r="K16" t="n">
-        <v>49.64333765536023</v>
+        <v>52.96127677749723</v>
       </c>
       <c r="L16" t="n">
-        <v>28.66210475734217</v>
+        <v>35.98819001297212</v>
       </c>
       <c r="M16" t="n">
-        <v>19.5714343709084</v>
+        <v>28.83101582323407</v>
       </c>
       <c r="N16" t="n">
-        <v>66.66879909216203</v>
+        <v>78.29091943178129</v>
       </c>
       <c r="O16" t="n">
-        <v>48.09976968490849</v>
+        <v>51.23036250161196</v>
       </c>
       <c r="P16" t="n">
-        <v>27.66326703785934</v>
+        <v>33.66639690058914</v>
       </c>
       <c r="Q16" t="n">
-        <v>26.57440586534099</v>
+        <v>32.22658482204344</v>
       </c>
       <c r="R16" t="n">
-        <v>25.44624673720125</v>
+        <v>30.61437313845215</v>
       </c>
       <c r="S16" t="n">
-        <v>27.84994115293288</v>
+        <v>34.62982854350997</v>
       </c>
     </row>
   </sheetData>
